--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radwan.mohamed\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80F06EA5-7EE7-4950-A543-F171E1F67D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9D733A5-CEFD-40D0-8E31-25B7CCE1A525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-900" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radwan.mohamed\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9D733A5-CEFD-40D0-8E31-25B7CCE1A525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{14C742B7-4B1C-40C1-B704-49C0DBD1B8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-900" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8110" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8110" uniqueCount="875">
   <si>
     <t>functional_code</t>
   </si>
@@ -2636,13 +2636,22 @@
     <t>device-ltj7ya8p0iemuckr942</t>
   </si>
   <si>
-    <t>2026-09-21T14:26:43.602Z</t>
-  </si>
-  <si>
-    <t>2026-09-21T14:41:14.714Z</t>
-  </si>
-  <si>
-    <t>2026-09-21T14:26:43.604Z</t>
+    <t>sep2026-1789997359027-aiy9yv7u</t>
+  </si>
+  <si>
+    <t>2026-09-21T13:29:19.027Z</t>
+  </si>
+  <si>
+    <t>2026-09-21T14:04:26.471Z</t>
+  </si>
+  <si>
+    <t>device-90cbbx1u5mrmubbgru0</t>
+  </si>
+  <si>
+    <t>18.7.6</t>
+  </si>
+  <si>
+    <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_7 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Version/18.7.6 Mobile/15E148 Safari/604.1</t>
   </si>
 </sst>
 </file>
@@ -2726,7 +2735,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -30481,7 +30501,7 @@
         <v>829</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="D129" s="11" t="s">
         <v>481</v>
@@ -32656,10 +32676,10 @@
     </row>
     <row r="146" spans="1:43">
       <c r="A146" s="10" t="s">
-        <v>776</v>
+        <v>869</v>
       </c>
       <c r="B146" s="10">
-        <v>30021979</v>
+        <v>30022376</v>
       </c>
       <c r="C146" s="10" t="s">
         <v>131</v>
@@ -32671,16 +32691,16 @@
         <v>46285</v>
       </c>
       <c r="F146" s="10" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="G146" s="12" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H146" s="10">
-        <v>871</v>
+        <v>2107</v>
       </c>
       <c r="I146" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J146" s="10" t="s">
         <v>34</v>
@@ -32698,16 +32718,16 @@
         <v>33</v>
       </c>
       <c r="O146" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P146" s="10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="Q146" s="10" t="s">
         <v>32</v>
       </c>
       <c r="R146" s="10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S146" s="10" t="s">
         <v>32</v>
@@ -32722,65 +32742,65 @@
         <v>33</v>
       </c>
       <c r="W146" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X146" s="10" t="s">
         <v>33</v>
       </c>
       <c r="Y146" s="10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Z146" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA146" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="AB146" s="10" t="s">
         <v>34</v>
       </c>
       <c r="AC146" s="10">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AD146" s="10">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AE146" s="10" t="s">
         <v>483</v>
       </c>
       <c r="AF146" s="10" t="s">
-        <v>777</v>
+        <v>872</v>
       </c>
       <c r="AG146" s="10"/>
       <c r="AH146" s="10" t="s">
-        <v>485</v>
+        <v>511</v>
       </c>
       <c r="AI146" s="10" t="s">
-        <v>604</v>
+        <v>873</v>
       </c>
       <c r="AJ146" s="10" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="AK146" s="10" t="s">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="AL146" s="10" t="s">
-        <v>605</v>
+        <v>874</v>
       </c>
       <c r="AM146" s="10">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="AN146" s="10">
-        <v>942</v>
+        <v>896</v>
       </c>
       <c r="AO146" s="10" t="s">
         <v>490</v>
       </c>
       <c r="AP146" s="10" t="s">
+        <v>870</v>
+      </c>
+      <c r="AQ146" s="10" t="s">
         <v>871</v>
-      </c>
-      <c r="AQ146" s="10" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="147" spans="1:43">
@@ -37054,6 +37074,9 @@
       <c r="AA1000" s="4"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B1000">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radwan.mohamed\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{14C742B7-4B1C-40C1-B704-49C0DBD1B8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1242CADD-31E3-470E-977B-54A82E91A8C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-900" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30579,10 +30579,10 @@
         <v>34</v>
       </c>
       <c r="AC129" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD129" s="10">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AE129" s="10" t="s">
         <v>483</v>
